--- a/outputs/evaluation/CF_M01_req_eval_gt_report.xlsx
+++ b/outputs/evaluation/CF_M01_req_eval_gt_report.xlsx
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.3483</v>
+        <v>0.3481</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.2428</v>
+        <v>0.2434</v>
       </c>
     </row>
     <row r="4">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.3222</v>
+        <v>0.3186</v>
       </c>
     </row>
     <row r="5">
@@ -618,11 +618,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>The system shall allow users with permissions to list the different connections of the players in the system.</t>
+          <t>The system shall allow users with permissions to list the different player connections of the system.</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.2979</v>
+        <v>0.2574</v>
       </c>
     </row>
     <row r="6">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.2963</v>
+        <v>0.2969</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/CF_M01_req_eval_gt_report.xlsx
+++ b/outputs/evaluation/CF_M01_req_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,12 +476,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M01_R25</t>
+          <t>CF_M01_R08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unauthorized users cannot access data they do not own.</t>
+          <t>All actions are performed on an entity of the platform.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -490,89 +490,97 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CF_M01_R024</t>
+          <t>CF_M01_R06</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>R_27</t>
+          <t>R_06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Users without permission shall not be able to access data for which they do not have permission.</t>
+          <t>The system shall store the actions performed on the platform.</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.3481</v>
+        <v>0.6781</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M01_R28</t>
+          <t>CF_M01_R11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A customer may have different users</t>
+          <t>You must be able to see all the details of the playlog.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Constraint</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CF_M01_R09</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>R_09</t>
+          <t>R_01</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>The system shall allow users with permissions to list the different playlogs of the system.</t>
+          <t>The system shall store the playlogs of the players.</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.2434</v>
+        <v>0.2495</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M01_R29</t>
+          <t>CF_M01_R17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The users are the ones who execute the actions in the platform</t>
+          <t>All actions must be related to an entity the platform.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Constraint</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CF_M01_R015</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
@@ -585,18 +593,18 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.3186</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M01_R30</t>
+          <t>CF_M01_R28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The users may have different players that reproduce contents</t>
+          <t>A customer may have different users</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -613,27 +621,27 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>R_12</t>
+          <t>R_09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>The system shall allow users with permissions to list the different player connections of the system.</t>
+          <t>The system shall allow users with permissions to list the different playlogs of the system.</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.2574</v>
+        <v>0.2366</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M01_R31</t>
+          <t>CF_M01_R29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Players are connected a given amount of time</t>
+          <t>The users are the ones who execute the actions in the platform</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -650,16 +658,90 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
+          <t>R_06</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>The system shall store the actions performed on the platform.</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.3462</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CF_M01_R30</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>The users may have different players that reproduce contents</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Constraint</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>R_12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>The system shall allow users with permissions to list the different player connections of the system.</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2545</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CF_M01_R31</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Players are connected a given amount of time</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Constraint</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>R_05</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>The connection status can only be connected or not connected.</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>0.2969</v>
+      <c r="K8" t="n">
+        <v>0.2924</v>
       </c>
     </row>
   </sheetData>
